--- a/data/trans_dic/P79$alquiler_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P79$alquiler_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,22</t>
+          <t>3,11; 11,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,4</t>
+          <t>2,05; 6,56</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,13</t>
+          <t>1,14; 5,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,27</t>
+          <t>2,34; 6,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,43</t>
+          <t>2,09; 4,86</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,71</t>
+          <t>3,25; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,24</t>
+          <t>1,69; 3,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,13</t>
+          <t>2,72; 4,99</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,24</t>
+          <t>0,93; 3,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,51</t>
+          <t>1,38; 3,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,97</t>
+          <t>1,37; 2,78</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,48</t>
+          <t>0,49; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,78</t>
+          <t>0,57; 2,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,22</t>
+          <t>0,74; 1,87</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,96</t>
+          <t>0,21; 1,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,71</t>
+          <t>0,2; 0,99</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,3</t>
+          <t>0,22; 1,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,07</t>
+          <t>0,19; 1,12</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,95</t>
+          <t>1,41; 2,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,49</t>
+          <t>1,88; 2,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,12</t>
+          <t>1,78; 2,54</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>26254</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 12865</t>
+          <t>0; 15083</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9890; 38257</t>
+          <t>10495; 38195</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11125; 42255</t>
+          <t>14683; 46928</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>30273</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3920; 21328</t>
+          <t>5330; 24250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7421; 22683</t>
+          <t>11342; 29771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15380; 37443</t>
+          <t>19888; 46313</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>44426</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11879; 29869</t>
+          <t>19474; 40262</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6564; 18731</t>
+          <t>10213; 24081</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22698; 45428</t>
+          <t>32806; 60148</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>26986</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3203; 19589</t>
+          <t>6317; 20998</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6655; 17424</t>
+          <t>9912; 22382</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11824; 30926</t>
+          <t>19204; 38838</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>13978</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>929; 8036</t>
+          <t>2892; 13974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2516; 9378</t>
+          <t>3348; 12043</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4266; 13098</t>
+          <t>8712; 22057</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3988</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3279</t>
+          <t>0; 4640</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>256; 5714</t>
+          <t>882; 5955</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1121; 6836</t>
+          <t>1650; 8115</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3649</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5577</t>
+          <t>0; 5968</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>867; 5268</t>
+          <t>970; 5872</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1224; 7345</t>
+          <t>1417; 8331</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>34323; 65621</t>
+          <t>48295; 85539</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48871; 87640</t>
+          <t>67680; 105514</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>90124; 146012</t>
+          <t>125300; 178156</t>
         </is>
       </c>
     </row>
